--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_19-01-2026.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='www.planetinsulation.co.uk', port=443): Max retries exceeded with url: /products/celotex-pir-tb-ga-xr?_pos=1&amp;_sid=22d5094c4&amp;_ss=r (Caused by SSLError(SSLEOFError(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1006)')))</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£24.75</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>£25.1</t>
+          <t>£24.99</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£32.98</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£40.45</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
